--- a/Global Arriendos/prueba bello asesor.xlsx
+++ b/Global Arriendos/prueba bello asesor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTADISTA_2\Documents\Portada Inmobiliaria\Inmuebles_Arrendados\Global Arriendos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19151301-AAEA-464A-8BE4-D65AF38B6320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C607D44E-B726-4176-A30A-C4214E77362F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="8964" xr2:uid="{9FCE5360-21BD-4F41-9FD3-77055D87F865}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9FCE5360-21BD-4F41-9FD3-77055D87F865}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -464,6 +464,21 @@
   </cellStyleXfs>
   <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -640,21 +655,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -986,385 +986,385 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="3" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="63" t="s">
+      <c r="C4" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="62" t="s">
+      <c r="D4" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="64" t="s">
+      <c r="E4" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="65" t="s">
+      <c r="F4" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="62" t="s">
+      <c r="G4" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="66" t="s">
+      <c r="H4" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="67" t="s">
+      <c r="I4" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="68" t="s">
+      <c r="J4" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62" t="s">
+      <c r="K4" s="67"/>
+      <c r="L4" s="67" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="21">
         <v>13008</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="22">
         <v>0.1</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="24">
         <v>1950000</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="7">
         <v>0.12</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="8">
         <f t="shared" ref="H5:H11" si="0">F5*G5</f>
         <v>234000</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
     </row>
     <row r="6" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="71"/>
-      <c r="B6" s="1" t="s">
+      <c r="A6" s="3"/>
+      <c r="B6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="21">
         <v>13009</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="22">
         <v>0.1</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="24">
         <v>1300000</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="8">
         <f t="shared" si="0"/>
         <v>91000.000000000015</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
     </row>
     <row r="7" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="71"/>
-      <c r="B7" s="1" t="s">
+      <c r="A7" s="3"/>
+      <c r="B7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="21">
         <v>13004</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="25">
         <v>0.1</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="24">
         <v>1200000</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="8">
         <f t="shared" si="0"/>
         <v>84000.000000000015</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
     </row>
     <row r="8" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="71"/>
-      <c r="B8" s="1" t="s">
+      <c r="A8" s="3"/>
+      <c r="B8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="26">
         <v>12973</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="27">
         <v>0.1</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="28">
         <v>1650000</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="14">
         <v>0.12</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="15">
         <f t="shared" si="0"/>
         <v>198000</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="I8" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
     </row>
     <row r="9" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="71"/>
-      <c r="B9" s="1" t="s">
+      <c r="A9" s="3"/>
+      <c r="B9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="31">
         <v>13062</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="27">
         <v>0.1</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="32">
         <v>1000000</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="17">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="18">
         <f t="shared" si="0"/>
         <v>70000</v>
       </c>
-      <c r="I9" s="28" t="s">
+      <c r="I9" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="29" t="s">
+      <c r="J9" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
     </row>
     <row r="10" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="71"/>
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="3"/>
+      <c r="B10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="26">
         <v>13101</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="27">
         <v>0.1</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="32">
         <v>1400000</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="17">
         <v>0.12</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="18">
         <f t="shared" si="0"/>
         <v>168000</v>
       </c>
-      <c r="I10" s="30" t="s">
+      <c r="I10" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="K10" s="32"/>
-      <c r="L10" s="33"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="38"/>
     </row>
     <row r="11" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="71"/>
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="3"/>
+      <c r="B11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="31">
         <v>13123</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="27">
         <v>0.1</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="32">
         <v>1350000</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="17">
         <v>0.12</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="18">
         <f t="shared" si="0"/>
         <v>162000</v>
       </c>
-      <c r="I11" s="28" t="s">
+      <c r="I11" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="29" t="s">
+      <c r="J11" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="K11" s="34"/>
-      <c r="L11" s="35"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="40"/>
     </row>
     <row r="12" spans="1:12" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="71"/>
-      <c r="B12" s="1" t="s">
+      <c r="A12" s="3"/>
+      <c r="B12" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="14" t="s">
+      <c r="D12" s="42"/>
+      <c r="E12" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="27"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="29" t="s">
+      <c r="F12" s="32"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15" t="s">
+      <c r="K12" s="20"/>
+      <c r="L12" s="20" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="71"/>
-      <c r="B13" s="1" t="s">
+      <c r="A13" s="3"/>
+      <c r="B13" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="14" t="s">
+      <c r="D13" s="42"/>
+      <c r="E13" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="27"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="29" t="s">
+      <c r="F13" s="32"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
     </row>
     <row r="14" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="71"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="45" t="s">
+      <c r="A14" s="3"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="46">
+      <c r="F14" s="51">
         <f>SUM(F5:F13)</f>
         <v>9850000</v>
       </c>
-      <c r="G14" s="47"/>
-      <c r="H14" s="48">
+      <c r="G14" s="52"/>
+      <c r="H14" s="53">
         <f>SUM(H5:H13)</f>
         <v>1007000</v>
       </c>
-      <c r="I14" s="49"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="51"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="56"/>
     </row>
     <row r="15" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="72"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="54" t="s">
+      <c r="A15" s="4"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="55">
+      <c r="F15" s="60">
         <f>H14+R14</f>
         <v>1007000</v>
       </c>
-      <c r="G15" s="53"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="59"/>
-      <c r="L15" s="60"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="3">
